--- a/docs/inputs/slope/xslope_nail_axial.xlsx
+++ b/docs/inputs/slope/xslope_nail_axial.xlsx
@@ -6142,13 +6142,13 @@
         <v>0.0</v>
       </c>
       <c r="AA11" s="3">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="3">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" s="3">
-        <v>2.744</v>
+        <v>0</v>
       </c>
       <c r="AD11" s="3">
         <v>0.0</v>
